--- a/files/港岛-香港仔及鸭脷洲-海盈山第4A期.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-海盈山第4A期.xlsx
@@ -3991,7 +3991,7 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>12538500</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>21544</v>
+        <v>21581</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>12538500</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>21544</v>
+        <v>21581</v>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
@@ -28593,9 +28593,9 @@
       </c>
       <c r="G14" s="23" t="inlineStr">
         <is>
-          <t>F | 582呎 (2房)
+          <t>F | 581呎 (2房)
 $1254万
-$21,544/呎
+$21,581/呎
 (25年-07月-08日)</t>
         </is>
       </c>

--- a/files/港岛-香港仔及鸭脷洲-海盈山第4A期.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-海盈山第4A期.xlsx
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="E311" s="4" t="n">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="F311" s="3" t="inlineStr">
         <is>
@@ -20037,7 +20037,7 @@
         <v>10182200</v>
       </c>
       <c r="I311" s="5" t="n">
-        <v>20951</v>
+        <v>20994</v>
       </c>
       <c r="J311" s="3" t="inlineStr">
         <is>
@@ -20048,7 +20048,7 @@
         <v>10182200</v>
       </c>
       <c r="L311" s="5" t="n">
-        <v>20951</v>
+        <v>20994</v>
       </c>
       <c r="M311" s="3" t="inlineStr">
         <is>
@@ -31106,9 +31106,9 @@
       </c>
       <c r="F21" s="23" t="inlineStr">
         <is>
-          <t>E | 486呎 (2房)
+          <t>E | 485呎 (2房)
 $1018万
-$20,951/呎
+$20,994/呎
 (25年-04月-28日)</t>
         </is>
       </c>

--- a/files/港岛-香港仔及鸭脷洲-海盈山第4A期.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-海盈山第4A期.xlsx
@@ -15169,7 +15169,7 @@
         </is>
       </c>
       <c r="E233" s="4" t="n">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>10725800</v>
       </c>
       <c r="I233" s="5" t="n">
-        <v>22070</v>
+        <v>22115</v>
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>10725800</v>
       </c>
       <c r="L233" s="5" t="n">
-        <v>22070</v>
+        <v>22115</v>
       </c>
       <c r="M233" s="3" t="inlineStr">
         <is>
@@ -30378,9 +30378,9 @@
       </c>
       <c r="F8" s="23" t="inlineStr">
         <is>
-          <t>E | 486呎 (2房)
+          <t>E | 485呎 (2房)
 $1073万
-$22,070/呎
+$22,115/呎
 (25年-07月-04日)</t>
         </is>
       </c>
